--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7,10 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="قطع_الغيار" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="صيانة_وقائية" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="الكرد" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="قطع_الغيار" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="صيانة_وقائية" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="الكرد" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="التفتيح" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="البرم" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="الغزل" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تمشيط" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ملفات" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="سحب اول" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="سحب ثاني" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="الضواغط" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="المكبس" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="المحطات" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,61 +425,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>اسم القطعة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>قوه الشد</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الرصيد الموجود</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>مدة التوريد</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ضرورية</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>القسم</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>رابط_الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>اسم القطعة</t>
+          <t>مده الاصلاح</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>المقاس</t>
+          <t>التاريخ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>قوه الشد</t>
+          <t>المعدة</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>الرصيد الموجود</t>
+          <t>الحدث/العطل</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>مدة التوريد</t>
+          <t>الإجراء التصحيحي</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ضرورية</t>
+          <t>تم بواسطة</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>القسم</t>
+          <t>قطع غيار مستخدمة</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>رابط_الصورة</t>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
         </is>
       </c>
     </row>
@@ -479,7 +546,220 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -532,6 +812,77 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>رابط_الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
         </is>
       </c>
     </row>
@@ -609,4 +960,359 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>